--- a/Design_Files/BOM/JLCPCB_BOM.xlsx
+++ b/Design_Files/BOM/JLCPCB_BOM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LiberDB\Documents\GitHub\manarharake-palmpcb\Design_Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="120">
   <si>
     <t>Comment</t>
   </si>
@@ -66,9 +66,6 @@
     <t>AFA07-S05FCC-00</t>
   </si>
   <si>
-    <t>2305018-2</t>
-  </si>
-  <si>
     <t>Blue</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
     <t>C2</t>
   </si>
   <si>
-    <t>C4, C5, C6, C7, C8, C9, C12, C15, C19, C21, C24, C25, C27</t>
-  </si>
-  <si>
     <t>C10</t>
   </si>
   <si>
@@ -174,9 +168,6 @@
     <t>J5, J6, J7, J8, J9, J10</t>
   </si>
   <si>
-    <t>J11</t>
-  </si>
-  <si>
     <t>LED1, LED2</t>
   </si>
   <si>
@@ -252,9 +243,6 @@
     <t>Sot-23</t>
   </si>
   <si>
-    <t>2305018-2_</t>
-  </si>
-  <si>
     <t>LED-0603</t>
   </si>
   <si>
@@ -321,9 +309,6 @@
     <t>C262339</t>
   </si>
   <si>
-    <t>C498674</t>
-  </si>
-  <si>
     <t>C158101</t>
   </si>
   <si>
@@ -382,6 +367,18 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>C165948</t>
+  </si>
+  <si>
+    <t>TYPE-C-31-M-12</t>
+  </si>
+  <si>
+    <t>C4, C5, C6, C7, C8, C9, C12, C15, C19, C24, C25, C27</t>
   </si>
 </sst>
 </file>
@@ -841,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -855,13 +852,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -869,13 +866,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -883,13 +880,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -897,13 +894,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -911,13 +908,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -925,13 +922,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -939,13 +936,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -953,13 +950,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -967,13 +964,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -981,13 +978,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -995,13 +992,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1009,13 +1006,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1023,13 +1020,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1037,13 +1034,13 @@
         <v>1729128</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" s="7">
         <v>1729128</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1051,13 +1048,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1065,279 +1062,279 @@
         <v>14</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>100</v>
+      <c r="A18" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Design_Files/BOM/JLCPCB_BOM.xlsx
+++ b/Design_Files/BOM/JLCPCB_BOM.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20410"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LiberDB\Documents\GitHub\manarharake-palmpcb\Design_Files\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarsVirgo\Documents\GitHub\manarharake-palmpcb\Design_Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CFC8DC-E1E5-490F-B5A7-A7BFC23FC063}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="118">
   <si>
     <t>Comment</t>
   </si>
@@ -141,9 +142,6 @@
     <t>C17</t>
   </si>
   <si>
-    <t>C22, C23, C29, C30</t>
-  </si>
-  <si>
     <t>C26, C28</t>
   </si>
   <si>
@@ -159,9 +157,6 @@
     <t>J1</t>
   </si>
   <si>
-    <t>J2</t>
-  </si>
-  <si>
     <t>J3</t>
   </si>
   <si>
@@ -216,9 +211,6 @@
     <t>U3, U4, U5</t>
   </si>
   <si>
-    <t>U13</t>
-  </si>
-  <si>
     <t>X1</t>
   </si>
   <si>
@@ -360,9 +352,6 @@
     <t>C882605</t>
   </si>
   <si>
-    <t>C7509570</t>
-  </si>
-  <si>
     <t>C2685197</t>
   </si>
   <si>
@@ -379,12 +368,18 @@
   </si>
   <si>
     <t>C4, C5, C6, C7, C8, C9, C12, C15, C19, C24, C25, C27</t>
+  </si>
+  <si>
+    <t>C22, C23</t>
+  </si>
+  <si>
+    <t>U6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -822,9 +817,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -841,10 +836,10 @@
         <v>33</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -855,10 +850,10 @@
         <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -869,10 +864,10 @@
         <v>35</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -880,13 +875,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -897,10 +892,10 @@
         <v>36</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -911,10 +906,10 @@
         <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -925,10 +920,10 @@
         <v>38</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -939,10 +934,10 @@
         <v>39</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -950,13 +945,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -964,13 +959,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -978,13 +973,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -992,13 +987,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1006,13 +1001,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1020,321 +1015,307 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>1729128</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="7">
-        <v>1729128</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>115</v>
+      <c r="C16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>14</v>
+        <v>112</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>118</v>
+        <v>47</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="5" t="s">
+      <c r="C34" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="6" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C35" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D35" s="4" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Design_Files/BOM/JLCPCB_BOM.xlsx
+++ b/Design_Files/BOM/JLCPCB_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarsVirgo\Documents\GitHub\manarharake-palmpcb\Design_Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CFC8DC-E1E5-490F-B5A7-A7BFC23FC063}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D9087D-5A78-4611-9D6E-A704D0BC7B93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,9 +64,6 @@
     <t>M Solder Pad</t>
   </si>
   <si>
-    <t>AFA07-S05FCC-00</t>
-  </si>
-  <si>
     <t>Blue</t>
   </si>
   <si>
@@ -187,9 +184,6 @@
     <t>R12, R14</t>
   </si>
   <si>
-    <t>R17</t>
-  </si>
-  <si>
     <t>R20</t>
   </si>
   <si>
@@ -298,9 +292,6 @@
     <t>C239643</t>
   </si>
   <si>
-    <t>C262339</t>
-  </si>
-  <si>
     <t>C158101</t>
   </si>
   <si>
@@ -374,6 +365,15 @@
   </si>
   <si>
     <t>U6</t>
+  </si>
+  <si>
+    <t>Ra</t>
+  </si>
+  <si>
+    <t>1.0-5PXJPZ</t>
+  </si>
+  <si>
+    <t>C31031</t>
   </si>
 </sst>
 </file>
@@ -833,13 +833,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -847,13 +847,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -861,13 +861,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -875,13 +875,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -889,13 +889,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -903,13 +903,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -917,13 +917,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -931,13 +931,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -945,13 +945,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -959,13 +959,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -973,13 +973,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -987,13 +987,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1001,13 +1001,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1015,13 +1015,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1029,293 +1029,293 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>14</v>
+      <c r="A16" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>92</v>
+        <v>45</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Design_Files/BOM/JLCPCB_BOM.xlsx
+++ b/Design_Files/BOM/JLCPCB_BOM.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20410"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MarsVirgo\Documents\GitHub\manarharake-palmpcb\Design_Files\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\manarharake-palmpcb\Design_Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D9087D-5A78-4611-9D6E-A704D0BC7B93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="119">
   <si>
     <t>Comment</t>
   </si>
@@ -64,6 +63,12 @@
     <t>M Solder Pad</t>
   </si>
   <si>
+    <t>TYPE-C-31-M-12</t>
+  </si>
+  <si>
+    <t>1.0-5PXJPZ</t>
+  </si>
+  <si>
     <t>Blue</t>
   </si>
   <si>
@@ -88,21 +93,21 @@
     <t>0R</t>
   </si>
   <si>
+    <t>1.2K</t>
+  </si>
+  <si>
+    <t>470R</t>
+  </si>
+  <si>
+    <t>22.1K</t>
+  </si>
+  <si>
+    <t>47.5K</t>
+  </si>
+  <si>
     <t>1M</t>
   </si>
   <si>
-    <t>1.2K</t>
-  </si>
-  <si>
-    <t>470R</t>
-  </si>
-  <si>
-    <t>22.1K</t>
-  </si>
-  <si>
-    <t>47.5K</t>
-  </si>
-  <si>
     <t>LP38692MP-5.0/NOPB</t>
   </si>
   <si>
@@ -127,6 +132,9 @@
     <t>C2</t>
   </si>
   <si>
+    <t>C4, C5, C6, C7, C8, C9, C12, C15, C19, C24, C25, C27</t>
+  </si>
+  <si>
     <t>C10</t>
   </si>
   <si>
@@ -139,6 +147,9 @@
     <t>C17</t>
   </si>
   <si>
+    <t>C22, C23</t>
+  </si>
+  <si>
     <t>C26, C28</t>
   </si>
   <si>
@@ -157,6 +168,9 @@
     <t>J3</t>
   </si>
   <si>
+    <t>J4</t>
+  </si>
+  <si>
     <t>J5, J6, J7, J8, J9, J10</t>
   </si>
   <si>
@@ -196,6 +210,9 @@
     <t>R24</t>
   </si>
   <si>
+    <t>Ra</t>
+  </si>
+  <si>
     <t>U1</t>
   </si>
   <si>
@@ -205,6 +222,9 @@
     <t>U3, U4, U5</t>
   </si>
   <si>
+    <t>U6</t>
+  </si>
+  <si>
     <t>X1</t>
   </si>
   <si>
@@ -229,6 +249,9 @@
     <t>Sot-23</t>
   </si>
   <si>
+    <t>TYPE-C-31-M-12_</t>
+  </si>
+  <si>
     <t>LED-0603</t>
   </si>
   <si>
@@ -292,6 +315,12 @@
     <t>C239643</t>
   </si>
   <si>
+    <t>C165948</t>
+  </si>
+  <si>
+    <t>C31031</t>
+  </si>
+  <si>
     <t>C158101</t>
   </si>
   <si>
@@ -313,21 +342,21 @@
     <t>C106231</t>
   </si>
   <si>
+    <t>C138040</t>
+  </si>
+  <si>
+    <t>C114877</t>
+  </si>
+  <si>
+    <t>C852648</t>
+  </si>
+  <si>
+    <t>C25896</t>
+  </si>
+  <si>
     <t>C105578</t>
   </si>
   <si>
-    <t>C138040</t>
-  </si>
-  <si>
-    <t>C114877</t>
-  </si>
-  <si>
-    <t>C852648</t>
-  </si>
-  <si>
-    <t>C25896</t>
-  </si>
-  <si>
     <t>C28191</t>
   </si>
   <si>
@@ -347,39 +376,12 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>J4</t>
-  </si>
-  <si>
-    <t>C165948</t>
-  </si>
-  <si>
-    <t>TYPE-C-31-M-12</t>
-  </si>
-  <si>
-    <t>C4, C5, C6, C7, C8, C9, C12, C15, C19, C24, C25, C27</t>
-  </si>
-  <si>
-    <t>C22, C23</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>Ra</t>
-  </si>
-  <si>
-    <t>1.0-5PXJPZ</t>
-  </si>
-  <si>
-    <t>C31031</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -817,7 +819,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -833,13 +835,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -847,13 +849,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -861,13 +863,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -875,13 +877,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -889,13 +891,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -903,13 +905,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -917,13 +919,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -931,13 +933,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -945,13 +947,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -959,13 +961,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -973,13 +975,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -987,13 +989,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1001,13 +1003,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1015,307 +1017,307 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>108</v>
+      <c r="D15" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>45</v>
+      <c r="A16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="s">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>106</v>
+      <c r="A35" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Design_Files/BOM/JLCPCB_BOM.xlsx
+++ b/Design_Files/BOM/JLCPCB_BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="118">
   <si>
     <t>Comment</t>
   </si>
@@ -66,9 +66,6 @@
     <t>TYPE-C-31-M-12</t>
   </si>
   <si>
-    <t>1.0-5PXJPZ</t>
-  </si>
-  <si>
     <t>Blue</t>
   </si>
   <si>
@@ -318,9 +315,6 @@
     <t>C165948</t>
   </si>
   <si>
-    <t>C31031</t>
-  </si>
-  <si>
     <t>C158101</t>
   </si>
   <si>
@@ -376,6 +370,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>SFW5R-1STE1LF</t>
   </si>
 </sst>
 </file>
@@ -835,13 +832,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -849,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -863,13 +860,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -877,13 +874,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -891,13 +888,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -905,13 +902,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -919,13 +916,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -933,13 +930,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -947,13 +944,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -961,13 +958,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -975,13 +972,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -989,13 +986,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1003,13 +1000,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1017,13 +1014,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1031,13 +1028,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1045,279 +1042,279 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="C17" s="7" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Design_Files/BOM/JLCPCB_BOM.xlsx
+++ b/Design_Files/BOM/JLCPCB_BOM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\manarharake-palmpcb\Design_Files\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LiberDB\Documents\GitHub\manarharake-palmpcb\Design_Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -51,9 +51,6 @@
     <t>PESD5V0H1BSFYL</t>
   </si>
   <si>
-    <t>B260A-13-F</t>
-  </si>
-  <si>
     <t>ESD5302F-3/TR</t>
   </si>
   <si>
@@ -240,9 +237,6 @@
     <t>DSN0603-2</t>
   </si>
   <si>
-    <t>SMA</t>
-  </si>
-  <si>
     <t>Sot-23</t>
   </si>
   <si>
@@ -306,9 +300,6 @@
     <t>C477989</t>
   </si>
   <si>
-    <t>C109094</t>
-  </si>
-  <si>
     <t>C239643</t>
   </si>
   <si>
@@ -373,6 +364,15 @@
   </si>
   <si>
     <t>SFW5R-1STE1LF</t>
+  </si>
+  <si>
+    <t>SMB</t>
+  </si>
+  <si>
+    <t>C3759253</t>
+  </si>
+  <si>
+    <t>SS54B-HF</t>
   </si>
 </sst>
 </file>
@@ -832,13 +832,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -846,13 +846,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -860,13 +860,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -874,13 +874,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -888,13 +888,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,13 +902,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -916,13 +916,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -930,13 +930,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -944,13 +944,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -958,13 +958,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -972,349 +972,349 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="C12" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>95</v>
+        <v>115</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
